--- a/РАБОЧИЙ СТОЛ/заказ дефицита по ПОКОМу КИ/дв 18,08,26 лгрсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/заказ дефицита по ПОКОМу КИ/дв 18,08,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\заказ дефицита по ПОКОМу КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\заказ дефицита по ПОКОМу КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673965DA-E542-4DC1-A99B-6E8D6FAA3E90}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFDDA6B-7B27-40D0-A9A8-2A257B19EC78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AJ$136</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -1443,6 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AW500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1706,7 +1699,7 @@
       <c r="AV3" s="1"/>
       <c r="AW3" s="1"/>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1792,7 +1785,7 @@
       <c r="AV4" s="1"/>
       <c r="AW4" s="1"/>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1920,7 +1913,7 @@
       <c r="AV5" s="1"/>
       <c r="AW5" s="1"/>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -2036,7 +2029,7 @@
         <v>45</v>
       </c>
       <c r="AM6" s="1">
-        <f t="shared" ref="AM6:AM37" si="9">(SUM(Y6:AH6)+R6)/11*G6</f>
+        <f t="shared" ref="AM6:AM36" si="9">(SUM(Y6:AH6)+R6)/11*G6</f>
         <v>496.69796363636362</v>
       </c>
       <c r="AN6" s="1"/>
@@ -2050,7 +2043,7 @@
       <c r="AV6" s="1"/>
       <c r="AW6" s="1"/>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>46</v>
       </c>
@@ -2178,7 +2171,7 @@
       <c r="AV7" s="1"/>
       <c r="AW7" s="1"/>
     </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>48</v>
       </c>
@@ -2306,7 +2299,7 @@
       <c r="AV8" s="1"/>
       <c r="AW8" s="1"/>
     </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>50</v>
       </c>
@@ -2418,7 +2411,7 @@
       <c r="AV9" s="1"/>
       <c r="AW9" s="1"/>
     </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -2540,7 +2533,7 @@
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
     </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>56</v>
       </c>
@@ -2668,7 +2661,7 @@
       <c r="AV11" s="1"/>
       <c r="AW11" s="1"/>
     </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
@@ -2793,7 +2786,7 @@
       <c r="AV12" s="1"/>
       <c r="AW12" s="1"/>
     </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>60</v>
       </c>
@@ -2918,7 +2911,7 @@
       <c r="AV13" s="1"/>
       <c r="AW13" s="1"/>
     </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>62</v>
       </c>
@@ -3043,7 +3036,7 @@
       <c r="AV14" s="1"/>
       <c r="AW14" s="1"/>
     </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>64</v>
       </c>
@@ -3157,7 +3150,7 @@
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
     </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
@@ -3281,7 +3274,7 @@
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
     </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>69</v>
       </c>
@@ -3411,7 +3404,7 @@
       <c r="AV17" s="1"/>
       <c r="AW17" s="1"/>
     </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>71</v>
       </c>
@@ -3536,7 +3529,7 @@
       <c r="AV18" s="1"/>
       <c r="AW18" s="1"/>
     </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>73</v>
       </c>
@@ -3661,7 +3654,7 @@
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
     </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>75</v>
       </c>
@@ -3785,7 +3778,7 @@
       <c r="AV20" s="1"/>
       <c r="AW20" s="1"/>
     </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>78</v>
       </c>
@@ -3913,7 +3906,7 @@
       <c r="AV21" s="1"/>
       <c r="AW21" s="1"/>
     </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -4038,7 +4031,7 @@
       <c r="AV22" s="1"/>
       <c r="AW22" s="1"/>
     </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>82</v>
       </c>
@@ -4163,7 +4156,7 @@
       <c r="AV23" s="1"/>
       <c r="AW23" s="1"/>
     </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>84</v>
       </c>
@@ -4275,7 +4268,7 @@
       <c r="AV24" s="1"/>
       <c r="AW24" s="1"/>
     </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>86</v>
       </c>
@@ -4512,8 +4505,8 @@
         <v>90</v>
       </c>
       <c r="AM26" s="1">
-        <f t="shared" si="9"/>
-        <v>21.288818181818179</v>
+        <f>30*G26</f>
+        <v>30</v>
       </c>
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
@@ -4526,7 +4519,7 @@
       <c r="AV26" s="1"/>
       <c r="AW26" s="1"/>
     </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>91</v>
       </c>
@@ -4761,8 +4754,8 @@
         <v>94</v>
       </c>
       <c r="AM28" s="1">
-        <f t="shared" si="9"/>
-        <v>31.975090909090909</v>
+        <f>40*G28</f>
+        <v>40</v>
       </c>
       <c r="AN28" s="1"/>
       <c r="AO28" s="1"/>
@@ -4888,8 +4881,8 @@
         <v>96</v>
       </c>
       <c r="AM29" s="1">
-        <f t="shared" si="9"/>
-        <v>391.4293454545454</v>
+        <f>450*G29</f>
+        <v>450</v>
       </c>
       <c r="AN29" s="1"/>
       <c r="AO29" s="1"/>
@@ -4902,7 +4895,7 @@
       <c r="AV29" s="1"/>
       <c r="AW29" s="1"/>
     </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>97</v>
       </c>
@@ -5020,7 +5013,7 @@
       <c r="AV30" s="1"/>
       <c r="AW30" s="1"/>
     </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
         <v>99</v>
       </c>
@@ -5251,8 +5244,8 @@
         <v>102</v>
       </c>
       <c r="AM32" s="1">
-        <f t="shared" si="9"/>
-        <v>326.29950909090911</v>
+        <f>600*G32</f>
+        <v>600</v>
       </c>
       <c r="AN32" s="1"/>
       <c r="AO32" s="1"/>
@@ -5265,7 +5258,7 @@
       <c r="AV32" s="1"/>
       <c r="AW32" s="1"/>
     </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
         <v>103</v>
       </c>
@@ -5503,7 +5496,7 @@
       <c r="AV34" s="1"/>
       <c r="AW34" s="1"/>
     </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>107</v>
       </c>
@@ -5615,7 +5608,7 @@
       <c r="AV35" s="1"/>
       <c r="AW35" s="1"/>
     </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>109</v>
       </c>
@@ -5854,7 +5847,7 @@
       <c r="AV37" s="1"/>
       <c r="AW37" s="1"/>
     </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>113</v>
       </c>
@@ -6091,8 +6084,8 @@
         <v>116</v>
       </c>
       <c r="AM39" s="1">
-        <f t="shared" si="18"/>
-        <v>79.170909090909092</v>
+        <f>220*G39</f>
+        <v>88</v>
       </c>
       <c r="AN39" s="1"/>
       <c r="AO39" s="1"/>
@@ -6227,7 +6220,7 @@
       <c r="AV40" s="1"/>
       <c r="AW40" s="1"/>
     </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>119</v>
       </c>
@@ -6352,7 +6345,7 @@
       <c r="AV41" s="1"/>
       <c r="AW41" s="1"/>
     </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>121</v>
       </c>
@@ -6585,8 +6578,8 @@
         <v>124</v>
       </c>
       <c r="AM43" s="1">
-        <f t="shared" si="18"/>
-        <v>9.8445454545454538</v>
+        <f>45*G43</f>
+        <v>15.749999999999998</v>
       </c>
       <c r="AN43" s="1"/>
       <c r="AO43" s="1"/>
@@ -6835,8 +6828,8 @@
         <v>128</v>
       </c>
       <c r="AM45" s="1">
-        <f t="shared" si="18"/>
-        <v>10.872727272727271</v>
+        <f>40*G45</f>
+        <v>16</v>
       </c>
       <c r="AN45" s="1"/>
       <c r="AO45" s="1"/>
@@ -6959,8 +6952,8 @@
         <v>130</v>
       </c>
       <c r="AM46" s="1">
-        <f t="shared" si="18"/>
-        <v>11.061818181818182</v>
+        <f>45*G46</f>
+        <v>18</v>
       </c>
       <c r="AN46" s="1"/>
       <c r="AO46" s="1"/>
@@ -6973,7 +6966,7 @@
       <c r="AV46" s="1"/>
       <c r="AW46" s="1"/>
     </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>131</v>
       </c>
@@ -7211,8 +7204,8 @@
         <v>134</v>
       </c>
       <c r="AM48" s="1">
-        <f t="shared" si="18"/>
-        <v>90.891818181818152</v>
+        <f>280*G48</f>
+        <v>98</v>
       </c>
       <c r="AN48" s="1"/>
       <c r="AO48" s="1"/>
@@ -7339,8 +7332,8 @@
         <v>136</v>
       </c>
       <c r="AM49" s="1">
-        <f t="shared" si="18"/>
-        <v>47.883636363636377</v>
+        <f>140*G49</f>
+        <v>56</v>
       </c>
       <c r="AN49" s="1"/>
       <c r="AO49" s="1"/>
@@ -7353,7 +7346,7 @@
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
     </row>
-    <row r="50" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>137</v>
       </c>
@@ -7478,7 +7471,7 @@
       <c r="AV50" s="1"/>
       <c r="AW50" s="1"/>
     </row>
-    <row r="51" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>139</v>
       </c>
@@ -7727,7 +7720,7 @@
       <c r="AV52" s="1"/>
       <c r="AW52" s="1"/>
     </row>
-    <row r="53" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>143</v>
       </c>
@@ -7849,7 +7842,7 @@
       <c r="AV53" s="1"/>
       <c r="AW53" s="1"/>
     </row>
-    <row r="54" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>145</v>
       </c>
@@ -8224,7 +8217,7 @@
       <c r="AV56" s="1"/>
       <c r="AW56" s="1"/>
     </row>
-    <row r="57" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>151</v>
       </c>
@@ -8349,7 +8342,7 @@
       <c r="AV57" s="1"/>
       <c r="AW57" s="1"/>
     </row>
-    <row r="58" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
         <v>153</v>
       </c>
@@ -8465,7 +8458,7 @@
       <c r="AV58" s="1"/>
       <c r="AW58" s="1"/>
     </row>
-    <row r="59" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>157</v>
       </c>
@@ -8587,7 +8580,7 @@
       <c r="AV59" s="1"/>
       <c r="AW59" s="1"/>
     </row>
-    <row r="60" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>159</v>
       </c>
@@ -8712,7 +8705,7 @@
       <c r="AV60" s="1"/>
       <c r="AW60" s="1"/>
     </row>
-    <row r="61" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>161</v>
       </c>
@@ -8839,7 +8832,7 @@
       <c r="AV61" s="1"/>
       <c r="AW61" s="1"/>
     </row>
-    <row r="62" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>163</v>
       </c>
@@ -8961,7 +8954,7 @@
       <c r="AV62" s="1"/>
       <c r="AW62" s="1"/>
     </row>
-    <row r="63" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>165</v>
       </c>
@@ -9086,7 +9079,7 @@
       <c r="AV63" s="1"/>
       <c r="AW63" s="1"/>
     </row>
-    <row r="64" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>167</v>
       </c>
@@ -9213,7 +9206,7 @@
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
     </row>
-    <row r="65" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>170</v>
       </c>
@@ -9340,7 +9333,7 @@
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
     </row>
-    <row r="66" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>172</v>
       </c>
@@ -9578,8 +9571,8 @@
         <v>175</v>
       </c>
       <c r="AM67" s="1">
-        <f>100*G67</f>
-        <v>40</v>
+        <f>130*G67</f>
+        <v>52</v>
       </c>
       <c r="AN67" s="1"/>
       <c r="AO67" s="1"/>
@@ -9844,7 +9837,7 @@
       <c r="AV69" s="1"/>
       <c r="AW69" s="1"/>
     </row>
-    <row r="70" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>180</v>
       </c>
@@ -9972,7 +9965,7 @@
       <c r="AV70" s="1"/>
       <c r="AW70" s="1"/>
     </row>
-    <row r="71" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>182</v>
       </c>
@@ -10097,7 +10090,7 @@
       <c r="AV71" s="1"/>
       <c r="AW71" s="1"/>
     </row>
-    <row r="72" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>184</v>
       </c>
@@ -10221,7 +10214,7 @@
       <c r="AV72" s="1"/>
       <c r="AW72" s="1"/>
     </row>
-    <row r="73" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>186</v>
       </c>
@@ -10346,7 +10339,7 @@
       <c r="AV73" s="1"/>
       <c r="AW73" s="1"/>
     </row>
-    <row r="74" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>188</v>
       </c>
@@ -10471,7 +10464,7 @@
       <c r="AV74" s="1"/>
       <c r="AW74" s="1"/>
     </row>
-    <row r="75" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>190</v>
       </c>
@@ -10596,7 +10589,7 @@
       <c r="AV75" s="1"/>
       <c r="AW75" s="1"/>
     </row>
-    <row r="76" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>192</v>
       </c>
@@ -10718,7 +10711,7 @@
       <c r="AV76" s="1"/>
       <c r="AW76" s="1"/>
     </row>
-    <row r="77" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>194</v>
       </c>
@@ -10842,7 +10835,7 @@
       <c r="AV77" s="1"/>
       <c r="AW77" s="1"/>
     </row>
-    <row r="78" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>196</v>
       </c>
@@ -10967,7 +10960,7 @@
       <c r="AV78" s="1"/>
       <c r="AW78" s="1"/>
     </row>
-    <row r="79" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>198</v>
       </c>
@@ -11092,7 +11085,7 @@
       <c r="AV79" s="1"/>
       <c r="AW79" s="1"/>
     </row>
-    <row r="80" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>200</v>
       </c>
@@ -11217,7 +11210,7 @@
       <c r="AV80" s="1"/>
       <c r="AW80" s="1"/>
     </row>
-    <row r="81" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>202</v>
       </c>
@@ -11341,7 +11334,7 @@
       <c r="AV81" s="1"/>
       <c r="AW81" s="1"/>
     </row>
-    <row r="82" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>204</v>
       </c>
@@ -11590,7 +11583,7 @@
       <c r="AV83" s="1"/>
       <c r="AW83" s="1"/>
     </row>
-    <row r="84" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>208</v>
       </c>
@@ -11712,7 +11705,7 @@
       <c r="AV84" s="1"/>
       <c r="AW84" s="1"/>
     </row>
-    <row r="85" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>210</v>
       </c>
@@ -11837,7 +11830,7 @@
       <c r="AV85" s="1"/>
       <c r="AW85" s="1"/>
     </row>
-    <row r="86" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>212</v>
       </c>
@@ -11959,7 +11952,7 @@
       <c r="AV86" s="1"/>
       <c r="AW86" s="1"/>
     </row>
-    <row r="87" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="9" t="s">
         <v>215</v>
       </c>
@@ -12077,7 +12070,7 @@
       <c r="AV87" s="1"/>
       <c r="AW87" s="1"/>
     </row>
-    <row r="88" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>217</v>
       </c>
@@ -12202,7 +12195,7 @@
       <c r="AV88" s="1"/>
       <c r="AW88" s="1"/>
     </row>
-    <row r="89" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>219</v>
       </c>
@@ -12327,7 +12320,7 @@
       <c r="AV89" s="1"/>
       <c r="AW89" s="1"/>
     </row>
-    <row r="90" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
         <v>221</v>
       </c>
@@ -12439,7 +12432,7 @@
       <c r="AV90" s="1"/>
       <c r="AW90" s="1"/>
     </row>
-    <row r="91" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>223</v>
       </c>
@@ -12566,7 +12559,7 @@
       <c r="AV91" s="1"/>
       <c r="AW91" s="1"/>
     </row>
-    <row r="92" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>225</v>
       </c>
@@ -12694,7 +12687,7 @@
       <c r="AV92" s="1"/>
       <c r="AW92" s="1"/>
     </row>
-    <row r="93" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>227</v>
       </c>
@@ -12824,7 +12817,7 @@
       <c r="AV93" s="1"/>
       <c r="AW93" s="1"/>
     </row>
-    <row r="94" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>229</v>
       </c>
@@ -12948,7 +12941,7 @@
       <c r="AV94" s="1"/>
       <c r="AW94" s="1"/>
     </row>
-    <row r="95" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="9" t="s">
         <v>231</v>
       </c>
@@ -13068,7 +13061,7 @@
       <c r="AV95" s="1"/>
       <c r="AW95" s="1"/>
     </row>
-    <row r="96" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
         <v>233</v>
       </c>
@@ -13291,8 +13284,8 @@
         <v>235</v>
       </c>
       <c r="AM97" s="1">
-        <f t="shared" si="27"/>
-        <v>12.327272727272728</v>
+        <f>60*G97</f>
+        <v>18</v>
       </c>
       <c r="AN97" s="1"/>
       <c r="AO97" s="1"/>
@@ -13305,7 +13298,7 @@
       <c r="AV97" s="1"/>
       <c r="AW97" s="1"/>
     </row>
-    <row r="98" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>236</v>
       </c>
@@ -13430,7 +13423,7 @@
       <c r="AV98" s="1"/>
       <c r="AW98" s="1"/>
     </row>
-    <row r="99" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
         <v>238</v>
       </c>
@@ -13668,7 +13661,7 @@
       <c r="AV100" s="1"/>
       <c r="AW100" s="1"/>
     </row>
-    <row r="101" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>242</v>
       </c>
@@ -13793,7 +13786,7 @@
       <c r="AV101" s="1"/>
       <c r="AW101" s="1"/>
     </row>
-    <row r="102" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
         <v>244</v>
       </c>
@@ -13913,7 +13906,7 @@
       <c r="AV102" s="1"/>
       <c r="AW102" s="1"/>
     </row>
-    <row r="103" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>246</v>
       </c>
@@ -14164,7 +14157,7 @@
       <c r="AV104" s="1"/>
       <c r="AW104" s="1"/>
     </row>
-    <row r="105" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
         <v>250</v>
       </c>
@@ -14276,7 +14269,7 @@
       <c r="AV105" s="1"/>
       <c r="AW105" s="1"/>
     </row>
-    <row r="106" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>252</v>
       </c>
@@ -14396,7 +14389,7 @@
       <c r="AV106" s="1"/>
       <c r="AW106" s="1"/>
     </row>
-    <row r="107" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>254</v>
       </c>
@@ -14521,7 +14514,7 @@
       <c r="AV107" s="1"/>
       <c r="AW107" s="1"/>
     </row>
-    <row r="108" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>256</v>
       </c>
@@ -14646,7 +14639,7 @@
       <c r="AV108" s="1"/>
       <c r="AW108" s="1"/>
     </row>
-    <row r="109" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>258</v>
       </c>
@@ -15149,7 +15142,7 @@
       <c r="AV112" s="1"/>
       <c r="AW112" s="1"/>
     </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
         <v>266</v>
       </c>
@@ -15261,7 +15254,7 @@
       <c r="AV113" s="1"/>
       <c r="AW113" s="1"/>
     </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>268</v>
       </c>
@@ -15383,7 +15376,7 @@
       <c r="AV114" s="1"/>
       <c r="AW114" s="1"/>
     </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>271</v>
       </c>
@@ -15508,7 +15501,7 @@
       <c r="AV115" s="1"/>
       <c r="AW115" s="1"/>
     </row>
-    <row r="116" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
         <v>273</v>
       </c>
@@ -15748,7 +15741,7 @@
       <c r="AV117" s="1"/>
       <c r="AW117" s="1"/>
     </row>
-    <row r="118" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>277</v>
       </c>
@@ -15871,7 +15864,7 @@
       <c r="AV118" s="1"/>
       <c r="AW118" s="1"/>
     </row>
-    <row r="119" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>280</v>
       </c>
@@ -15995,7 +15988,7 @@
       <c r="AV119" s="1"/>
       <c r="AW119" s="1"/>
     </row>
-    <row r="120" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>282</v>
       </c>
@@ -16117,7 +16110,7 @@
       <c r="AV120" s="1"/>
       <c r="AW120" s="1"/>
     </row>
-    <row r="121" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>284</v>
       </c>
@@ -16240,7 +16233,7 @@
       <c r="AV121" s="1"/>
       <c r="AW121" s="1"/>
     </row>
-    <row r="122" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="9" t="s">
         <v>286</v>
       </c>
@@ -16352,7 +16345,7 @@
       <c r="AV122" s="1"/>
       <c r="AW122" s="1"/>
     </row>
-    <row r="123" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>288</v>
       </c>
@@ -16477,7 +16470,7 @@
       <c r="AV123" s="1"/>
       <c r="AW123" s="1"/>
     </row>
-    <row r="124" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>290</v>
       </c>
@@ -16602,7 +16595,7 @@
       <c r="AV124" s="1"/>
       <c r="AW124" s="1"/>
     </row>
-    <row r="125" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>292</v>
       </c>
@@ -16727,7 +16720,7 @@
       <c r="AV125" s="1"/>
       <c r="AW125" s="1"/>
     </row>
-    <row r="126" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>294</v>
       </c>
@@ -17102,7 +17095,7 @@
       <c r="AV128" s="1"/>
       <c r="AW128" s="1"/>
     </row>
-    <row r="129" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>301</v>
       </c>
@@ -17336,8 +17329,8 @@
         <v>304</v>
       </c>
       <c r="AM130" s="1">
-        <f t="shared" si="37"/>
-        <v>23.852727272727265</v>
+        <f>95*G130</f>
+        <v>28.5</v>
       </c>
       <c r="AN130" s="1"/>
       <c r="AO130" s="1"/>
@@ -17458,8 +17451,8 @@
         <v>306</v>
       </c>
       <c r="AM131" s="1">
-        <f t="shared" si="37"/>
-        <v>17.280000000000005</v>
+        <f>70*G131</f>
+        <v>21</v>
       </c>
       <c r="AN131" s="1"/>
       <c r="AO131" s="1"/>
@@ -17472,7 +17465,7 @@
       <c r="AV131" s="1"/>
       <c r="AW131" s="1"/>
     </row>
-    <row r="132" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>307</v>
       </c>
@@ -17709,8 +17702,8 @@
         <v>310</v>
       </c>
       <c r="AM133" s="1">
-        <f t="shared" si="37"/>
-        <v>15.065454545454546</v>
+        <f>60*G133</f>
+        <v>18</v>
       </c>
       <c r="AN133" s="1"/>
       <c r="AO133" s="1"/>
@@ -17847,7 +17840,7 @@
       <c r="AV134" s="1"/>
       <c r="AW134" s="1"/>
     </row>
-    <row r="135" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="9" t="s">
         <v>313</v>
       </c>
@@ -17958,7 +17951,7 @@
       <c r="AV135" s="1"/>
       <c r="AW135" s="1"/>
     </row>
-    <row r="136" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:49" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="9" t="s">
         <v>315</v>
       </c>
@@ -36270,7 +36263,13 @@
       <c r="AW500" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AJ136" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AJ136" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="8">
+      <filters>
+        <filter val="НЕДОГРУЗ / матрица"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>
